--- a/site/ADP-Lyric-HCM-to-Pinpoint-Integration-Guide/headings.xlsx
+++ b/site/ADP-Lyric-HCM-to-Pinpoint-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,22 +507,682 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Integration Setup</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>h_01KKE0CXZEC4VH5J2HJBMJ079M</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Lyric-HCM-to-Pinpoint-Integration-Guide/#h_01KKE0CXZEC4VH5J2HJBMJ079M</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>Create Integration</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>H3</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>h_01KKDX8VVJ00F90N9QF616KJHS</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Lyric-HCM-to-Pinpoint-Integration-Guide/#h_01KKDX8VVJ00F90N9QF616KJHS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Configuration</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>h_01KKE0TG61GAQB4D6WE3WHC9PY</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Lyric-HCM-to-Pinpoint-Integration-Guide/#h_01KKE0TG61GAQB4D6WE3WHC9PY</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Applications</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>h_01KKE0TG6267D3PYXXD4RR5EMT</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Lyric-HCM-to-Pinpoint-Integration-Guide/#h_01KKE0TG6267D3PYXXD4RR5EMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Parameters</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>h_01KKE0TG62CPQ23B5SYFAT8CZE</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Lyric-HCM-to-Pinpoint-Integration-Guide/#h_01KKE0TG62CPQ23B5SYFAT8CZE</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Integration Scenarios</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>h_01KKE0TG63ESGQ430FTKG5S1CV</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Lyric-HCM-to-Pinpoint-Integration-Guide/#h_01KKE0TG63ESGQ430FTKG5S1CV</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>General Settings</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>h_01KKE1276FGBNKK84C627GJM7N</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Lyric-HCM-to-Pinpoint-Integration-Guide/#h_01KKE1276FGBNKK84C627GJM7N</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Onboarding</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>h_01KKE3AKCQY45QBJ7YWF8EB2H9</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Lyric-HCM-to-Pinpoint-Integration-Guide/#h_01KKE3AKCQY45QBJ7YWF8EB2H9</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Onboarding field validation</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>h_01KKE3AKCQYBDFJ27B51RV06GY</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Lyric-HCM-to-Pinpoint-Integration-Guide/#h_01KKE3AKCQYBDFJ27B51RV06GY</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Sensitive Data</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>h_01KKE3AKCRGD8WENM5WZ0Z533Y</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Lyric-HCM-to-Pinpoint-Integration-Guide/#h_01KKE3AKCRGD8WENM5WZ0Z533Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Sensitive data masking settings</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>h_01KKE3AKCRFZ5JCBC3B117NS68</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Lyric-HCM-to-Pinpoint-Integration-Guide/#h_01KKE3AKCRFZ5JCBC3B117NS68</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Log Settings</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>h_01KKE3AKCSE6PMHF0J3NEJ9TY0</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Lyric-HCM-to-Pinpoint-Integration-Guide/#h_01KKE3AKCSE6PMHF0J3NEJ9TY0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Report Settings</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>h_01KKE3AKCVBDZF56RRNHH8TTQT</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Lyric-HCM-to-Pinpoint-Integration-Guide/#h_01KKE3AKCVBDZF56RRNHH8TTQT</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Email Notification Configuration</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>h_01KKE51MQSHG7VBCVP33WYY0V7</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Lyric-HCM-to-Pinpoint-Integration-Guide/#h_01KKE51MQSHG7VBCVP33WYY0V7</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Notification Triggers</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>h_01KKE530Y3MEAW93TTE6R2NKSE</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Lyric-HCM-to-Pinpoint-Integration-Guide/#h_01KKE530Y3MEAW93TTE6R2NKSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Success Notification Settings</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>h_01KKE5373G2MRKHGERX9QQ22HK</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Lyric-HCM-to-Pinpoint-Integration-Guide/#h_01KKE5373G2MRKHGERX9QQ22HK</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Failure Notification Settings</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>h_01KKE51MQT8SE9VXTSMR9FYX47</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Lyric-HCM-to-Pinpoint-Integration-Guide/#h_01KKE51MQT8SE9VXTSMR9FYX47</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Skipped Records Notification Settings</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>h_01KKE51MQVZJ1BS650MQDMM551</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Lyric-HCM-to-Pinpoint-Integration-Guide/#h_01KKE51MQVZJ1BS650MQDMM551</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Notification Report Settings</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>h_01KKE51MQV606ZTXH40HDR9V4H</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Lyric-HCM-to-Pinpoint-Integration-Guide/#h_01KKE51MQV606ZTXH40HDR9V4H</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Log insights</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>h_01KKE5C8R7NSMZ9YNKDXNCQW8Y</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Lyric-HCM-to-Pinpoint-Integration-Guide/#h_01KKE5C8R7NSMZ9YNKDXNCQW8Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Attribute Map</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>h_01KKE5KQM36N8CGKNPXMR40JB9</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Lyric-HCM-to-Pinpoint-Integration-Guide/#h_01KKE5KQM36N8CGKNPXMR40JB9</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Modify attribute mappings</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>h_01KKE5KQM48ESP2C2Q4GHQYZ7V</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Lyric-HCM-to-Pinpoint-Integration-Guide/#h_01KKE5KQM48ESP2C2Q4GHQYZ7V</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Required fields</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>h_01KKE5KQM4X9KRD3R130RYQSEN</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Lyric-HCM-to-Pinpoint-Integration-Guide/#h_01KKE5KQM4X9KRD3R130RYQSEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Save mapping changes</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>h_01KKE5KQM5AJB1SMMM2ZY6V4RK</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Lyric-HCM-to-Pinpoint-Integration-Guide/#h_01KKE5KQM5AJB1SMMM2ZY6V4RK</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Tables</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>h_01KKE5VFWMFS4MGW39XRY696W5</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Lyric-HCM-to-Pinpoint-Integration-Guide/#h_01KKE5VFWMFS4MGW39XRY696W5</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Available Tables</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>h_01KKE5VFWPK29TCZE7CDJ75R03</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Lyric-HCM-to-Pinpoint-Integration-Guide/#h_01KKE5VFWPK29TCZE7CDJ75R03</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Managing Table Data</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>h_01KKE5XDHQBFHAV6DYC811B8DW</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Lyric-HCM-to-Pinpoint-Integration-Guide/#h_01KKE5XDHQBFHAV6DYC811B8DW</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>h_01KKE5XDHR4GEAWTR2ZVRW2DC5</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Lyric-HCM-to-Pinpoint-Integration-Guide/#h_01KKE5XDHR4GEAWTR2ZVRW2DC5</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>h_01KKE5XDHSY1F6XYQF0A6TJE46</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Lyric-HCM-to-Pinpoint-Integration-Guide/#h_01KKE5XDHSY1F6XYQF0A6TJE46</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Additional Options</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>h_01KKE5XDHS33F0K412JG7Q8WHG</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Lyric-HCM-to-Pinpoint-Integration-Guide/#h_01KKE5XDHS33F0K412JG7Q8WHG</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Update the Integration to the Latest Version</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>h_01KKE5Z8PGRHXBEY08YRF828VV</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Lyric-HCM-to-Pinpoint-Integration-Guide/#h_01KKE5Z8PGRHXBEY08YRF828VV</t>
         </is>
       </c>
     </row>
